--- a/summary_odp_black_special_value_hq.xlsx
+++ b/summary_odp_black_special_value_hq.xlsx
@@ -525,16 +525,16 @@
         <v>42</v>
       </c>
       <c r="D2">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E2">
-        <v>83.3</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="F2">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="G2">
-        <v>3.4</v>
+        <v>3.17</v>
       </c>
       <c r="H2">
         <v>31</v>
@@ -575,10 +575,10 @@
         <v>100</v>
       </c>
       <c r="F3">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G3">
-        <v>5.73</v>
+        <v>5.82</v>
       </c>
       <c r="H3">
         <v>5</v>
@@ -657,16 +657,16 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E5">
-        <v>75.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="F5">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G5">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="H5">
         <v>25</v>
@@ -707,10 +707,10 @@
         <v>100</v>
       </c>
       <c r="F6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="H6">
         <v>5</v>
@@ -833,16 +833,16 @@
         <v>29</v>
       </c>
       <c r="D9">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E9">
-        <v>75.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="F9">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G9">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="H9">
         <v>25</v>
@@ -1009,16 +1009,16 @@
         <v>19</v>
       </c>
       <c r="D13">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E13">
-        <v>63.2</v>
+        <v>94.7</v>
       </c>
       <c r="F13">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G13">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="H13">
         <v>17</v>
@@ -1103,10 +1103,10 @@
         <v>100</v>
       </c>
       <c r="F15">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G15">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="H15">
         <v>5</v>

--- a/summary_odp_black_special_value_hq.xlsx
+++ b/summary_odp_black_special_value_hq.xlsx
@@ -531,10 +531,10 @@
         <v>97.59999999999999</v>
       </c>
       <c r="F2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G2">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="H2">
         <v>31</v>
@@ -663,10 +663,10 @@
         <v>96.59999999999999</v>
       </c>
       <c r="F5">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G5">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="H5">
         <v>25</v>
@@ -839,10 +839,10 @@
         <v>96.59999999999999</v>
       </c>
       <c r="F9">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G9">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="H9">
         <v>25</v>
@@ -971,10 +971,10 @@
         <v>100</v>
       </c>
       <c r="F12">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G12">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="H12">
         <v>5</v>

--- a/summary_odp_black_special_value_hq.xlsx
+++ b/summary_odp_black_special_value_hq.xlsx
@@ -537,16 +537,16 @@
         <v>3.2</v>
       </c>
       <c r="H2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I2">
-        <v>73.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K2">
-        <v>16.7</v>
+        <v>19</v>
       </c>
       <c r="L2">
         <v>4</v>
@@ -555,7 +555,7 @@
         <v>9.5</v>
       </c>
       <c r="N2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -581,16 +581,16 @@
         <v>5.82</v>
       </c>
       <c r="H3">
+        <v>4</v>
+      </c>
+      <c r="I3">
+        <v>36.4</v>
+      </c>
+      <c r="J3">
         <v>5</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>45.5</v>
-      </c>
-      <c r="J3">
-        <v>4</v>
-      </c>
-      <c r="K3">
-        <v>36.4</v>
       </c>
       <c r="L3">
         <v>2</v>
@@ -599,7 +599,7 @@
         <v>18.2</v>
       </c>
       <c r="N3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -713,16 +713,16 @@
         <v>6.1</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I6">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L6">
         <v>2</v>
@@ -731,7 +731,7 @@
         <v>20</v>
       </c>
       <c r="N6">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1109,16 +1109,16 @@
         <v>6.1</v>
       </c>
       <c r="H15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I15">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L15">
         <v>2</v>
@@ -1127,7 +1127,7 @@
         <v>20</v>
       </c>
       <c r="N15">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/summary_odp_black_special_value_hq.xlsx
+++ b/summary_odp_black_special_value_hq.xlsx
@@ -531,10 +531,10 @@
         <v>97.59999999999999</v>
       </c>
       <c r="F2">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="G2">
-        <v>3.2</v>
+        <v>3.83</v>
       </c>
       <c r="H2">
         <v>30</v>
@@ -575,10 +575,10 @@
         <v>100</v>
       </c>
       <c r="F3">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="G3">
-        <v>5.82</v>
+        <v>8.18</v>
       </c>
       <c r="H3">
         <v>4</v>
@@ -707,10 +707,10 @@
         <v>100</v>
       </c>
       <c r="F6">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="G6">
-        <v>6.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H6">
         <v>4</v>
@@ -1103,10 +1103,10 @@
         <v>100</v>
       </c>
       <c r="F15">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="G15">
-        <v>6.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H15">
         <v>4</v>

--- a/summary_odp_black_special_value_hq.xlsx
+++ b/summary_odp_black_special_value_hq.xlsx
@@ -525,16 +525,16 @@
         <v>42</v>
       </c>
       <c r="D2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E2">
-        <v>97.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="F2">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="G2">
-        <v>3.83</v>
+        <v>4.33</v>
       </c>
       <c r="H2">
         <v>30</v>
@@ -575,10 +575,10 @@
         <v>100</v>
       </c>
       <c r="F3">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="G3">
-        <v>8.18</v>
+        <v>9.73</v>
       </c>
       <c r="H3">
         <v>4</v>
@@ -657,16 +657,16 @@
         <v>29</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="F5">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G5">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="H5">
         <v>25</v>
@@ -707,10 +707,10 @@
         <v>100</v>
       </c>
       <c r="F6">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G6">
-        <v>8.699999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="H6">
         <v>4</v>
@@ -833,16 +833,16 @@
         <v>29</v>
       </c>
       <c r="D9">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E9">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="F9">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="G9">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="H9">
         <v>25</v>
@@ -1009,16 +1009,16 @@
         <v>19</v>
       </c>
       <c r="D13">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E13">
-        <v>94.7</v>
+        <v>100</v>
       </c>
       <c r="F13">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G13">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="H13">
         <v>17</v>
@@ -1059,10 +1059,10 @@
         <v>100</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G14">
-        <v>1.25</v>
+        <v>2.75</v>
       </c>
       <c r="H14">
         <v>3</v>
@@ -1103,10 +1103,10 @@
         <v>100</v>
       </c>
       <c r="F15">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G15">
-        <v>8.699999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="H15">
         <v>4</v>

--- a/summary_odp_black_special_value_hq.xlsx
+++ b/summary_odp_black_special_value_hq.xlsx
@@ -531,10 +531,10 @@
         <v>100</v>
       </c>
       <c r="F2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G2">
-        <v>4.33</v>
+        <v>4.36</v>
       </c>
       <c r="H2">
         <v>30</v>
@@ -663,10 +663,10 @@
         <v>100</v>
       </c>
       <c r="F5">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G5">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="H5">
         <v>25</v>
@@ -839,10 +839,10 @@
         <v>100</v>
       </c>
       <c r="F9">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G9">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="H9">
         <v>25</v>
@@ -1015,10 +1015,10 @@
         <v>100</v>
       </c>
       <c r="F13">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G13">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="H13">
         <v>17</v>

--- a/summary_odp_black_special_value_hq.xlsx
+++ b/summary_odp_black_special_value_hq.xlsx
@@ -537,25 +537,25 @@
         <v>4.36</v>
       </c>
       <c r="H2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I2">
-        <v>71.40000000000001</v>
+        <v>69</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K2">
-        <v>19</v>
+        <v>16.7</v>
       </c>
       <c r="L2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M2">
-        <v>9.5</v>
+        <v>14.3</v>
       </c>
       <c r="N2">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -581,25 +581,25 @@
         <v>9.73</v>
       </c>
       <c r="H3">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>27.3</v>
+      </c>
+      <c r="J3">
         <v>4</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <v>36.4</v>
       </c>
-      <c r="J3">
-        <v>5</v>
-      </c>
-      <c r="K3">
-        <v>45.5</v>
-      </c>
       <c r="L3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M3">
-        <v>18.2</v>
+        <v>36.4</v>
       </c>
       <c r="N3">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -713,25 +713,25 @@
         <v>10.4</v>
       </c>
       <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>30</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6">
+        <v>30</v>
+      </c>
+      <c r="L6">
         <v>4</v>
       </c>
-      <c r="I6">
+      <c r="M6">
         <v>40</v>
       </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>40</v>
-      </c>
-      <c r="L6">
-        <v>2</v>
-      </c>
-      <c r="M6">
-        <v>20</v>
-      </c>
       <c r="N6">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1109,25 +1109,25 @@
         <v>10.4</v>
       </c>
       <c r="H15">
+        <v>3</v>
+      </c>
+      <c r="I15">
+        <v>30</v>
+      </c>
+      <c r="J15">
+        <v>3</v>
+      </c>
+      <c r="K15">
+        <v>30</v>
+      </c>
+      <c r="L15">
         <v>4</v>
       </c>
-      <c r="I15">
+      <c r="M15">
         <v>40</v>
       </c>
-      <c r="J15">
-        <v>4</v>
-      </c>
-      <c r="K15">
-        <v>40</v>
-      </c>
-      <c r="L15">
-        <v>2</v>
-      </c>
-      <c r="M15">
-        <v>20</v>
-      </c>
       <c r="N15">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/summary_odp_black_special_value_hq.xlsx
+++ b/summary_odp_black_special_value_hq.xlsx
@@ -531,10 +531,10 @@
         <v>100</v>
       </c>
       <c r="F2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G2">
-        <v>4.36</v>
+        <v>4.4</v>
       </c>
       <c r="H2">
         <v>29</v>
@@ -663,10 +663,10 @@
         <v>100</v>
       </c>
       <c r="F5">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G5">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="H5">
         <v>25</v>
@@ -839,10 +839,10 @@
         <v>100</v>
       </c>
       <c r="F9">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G9">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="H9">
         <v>25</v>
@@ -971,10 +971,10 @@
         <v>100</v>
       </c>
       <c r="F12">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G12">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="H12">
         <v>5</v>
@@ -1015,10 +1015,10 @@
         <v>100</v>
       </c>
       <c r="F13">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G13">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="H13">
         <v>17</v>

--- a/summary_odp_black_special_value_hq.xlsx
+++ b/summary_odp_black_special_value_hq.xlsx
@@ -537,16 +537,16 @@
         <v>4.4</v>
       </c>
       <c r="H2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I2">
-        <v>69</v>
+        <v>66.7</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K2">
-        <v>16.7</v>
+        <v>19</v>
       </c>
       <c r="L2">
         <v>6</v>
@@ -555,7 +555,7 @@
         <v>14.3</v>
       </c>
       <c r="N2">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -581,16 +581,16 @@
         <v>9.73</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>27.3</v>
+        <v>18.2</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3">
-        <v>36.4</v>
+        <v>45.5</v>
       </c>
       <c r="L3">
         <v>4</v>
@@ -599,7 +599,7 @@
         <v>36.4</v>
       </c>
       <c r="N3">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -713,16 +713,16 @@
         <v>10.4</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L6">
         <v>4</v>
@@ -731,7 +731,7 @@
         <v>40</v>
       </c>
       <c r="N6">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1109,16 +1109,16 @@
         <v>10.4</v>
       </c>
       <c r="H15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I15">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L15">
         <v>4</v>
@@ -1127,7 +1127,7 @@
         <v>40</v>
       </c>
       <c r="N15">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/summary_odp_black_special_value_hq.xlsx
+++ b/summary_odp_black_special_value_hq.xlsx
@@ -555,7 +555,7 @@
         <v>14.3</v>
       </c>
       <c r="N2">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -599,7 +599,7 @@
         <v>36.4</v>
       </c>
       <c r="N3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -731,7 +731,7 @@
         <v>40</v>
       </c>
       <c r="N6">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1127,7 +1127,7 @@
         <v>40</v>
       </c>
       <c r="N15">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/summary_odp_black_special_value_hq.xlsx
+++ b/summary_odp_black_special_value_hq.xlsx
@@ -543,19 +543,19 @@
         <v>66.7</v>
       </c>
       <c r="J2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K2">
-        <v>19</v>
+        <v>28.6</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>14.3</v>
+        <v>4.8</v>
       </c>
       <c r="N2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -587,19 +587,19 @@
         <v>18.2</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K3">
-        <v>45.5</v>
+        <v>72.7</v>
       </c>
       <c r="L3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>36.4</v>
+        <v>9.1</v>
       </c>
       <c r="N3">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -631,16 +631,16 @@
         <v>50</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -719,19 +719,19 @@
         <v>20</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="L6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="N6">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -807,16 +807,16 @@
         <v>50</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -939,16 +939,16 @@
         <v>50</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -1115,19 +1115,19 @@
         <v>20</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="L15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M15">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="N15">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/summary_odp_black_special_value_hq.xlsx
+++ b/summary_odp_black_special_value_hq.xlsx
@@ -531,10 +531,10 @@
         <v>100</v>
       </c>
       <c r="F2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G2">
-        <v>4.4</v>
+        <v>4.43</v>
       </c>
       <c r="H2">
         <v>28</v>
@@ -663,10 +663,10 @@
         <v>100</v>
       </c>
       <c r="F5">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G5">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="H5">
         <v>25</v>
@@ -839,10 +839,10 @@
         <v>100</v>
       </c>
       <c r="F9">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G9">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="H9">
         <v>25</v>
@@ -971,10 +971,10 @@
         <v>100</v>
       </c>
       <c r="F12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G12">
-        <v>2.67</v>
+        <v>2.83</v>
       </c>
       <c r="H12">
         <v>5</v>

--- a/summary_odp_black_special_value_hq.xlsx
+++ b/summary_odp_black_special_value_hq.xlsx
@@ -537,16 +537,16 @@
         <v>4.43</v>
       </c>
       <c r="H2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I2">
-        <v>66.7</v>
+        <v>64.3</v>
       </c>
       <c r="J2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K2">
-        <v>28.6</v>
+        <v>31</v>
       </c>
       <c r="L2">
         <v>2</v>
@@ -555,7 +555,7 @@
         <v>4.8</v>
       </c>
       <c r="N2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -669,16 +669,16 @@
         <v>1.97</v>
       </c>
       <c r="H5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I5">
-        <v>86.2</v>
+        <v>82.8</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5">
-        <v>10.3</v>
+        <v>13.8</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -687,7 +687,7 @@
         <v>3.4</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -845,16 +845,16 @@
         <v>1.97</v>
       </c>
       <c r="H9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I9">
-        <v>86.2</v>
+        <v>82.8</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K9">
-        <v>10.3</v>
+        <v>13.8</v>
       </c>
       <c r="L9">
         <v>1</v>
@@ -863,7 +863,7 @@
         <v>3.4</v>
       </c>
       <c r="N9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1021,16 +1021,16 @@
         <v>1.53</v>
       </c>
       <c r="H13">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I13">
-        <v>89.5</v>
+        <v>84.2</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K13">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="L13">
         <v>1</v>
@@ -1039,7 +1039,7 @@
         <v>5.3</v>
       </c>
       <c r="N13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:14">

--- a/summary_odp_black_special_value_hq.xlsx
+++ b/summary_odp_black_special_value_hq.xlsx
@@ -531,10 +531,10 @@
         <v>100</v>
       </c>
       <c r="F2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G2">
-        <v>4.43</v>
+        <v>4.45</v>
       </c>
       <c r="H2">
         <v>27</v>
@@ -663,10 +663,10 @@
         <v>100</v>
       </c>
       <c r="F5">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G5">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="H5">
         <v>24</v>
@@ -839,10 +839,10 @@
         <v>100</v>
       </c>
       <c r="F9">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G9">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="H9">
         <v>24</v>
@@ -1015,10 +1015,10 @@
         <v>100</v>
       </c>
       <c r="F13">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G13">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="H13">
         <v>16</v>
